--- a/output/pdf_financials_xlsx/VEC.H.xlsx
+++ b/output/pdf_financials_xlsx/VEC.H.xlsx
@@ -5655,52 +5655,52 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>5.992926</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>6.540866</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>6.540866</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>6.602497</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>7.053341</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>7.088342</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>7.145685</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>7.594799</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>7.594799</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>7.734318</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>7.734318</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>7.734318</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>7.734318</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>7.734318</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>7.734318</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>7.734318</v>
       </c>
     </row>
     <row r="93">
@@ -7084,34 +7084,34 @@
         </is>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-3.647901</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>23.206664</v>
+        <v>20.161011</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.330163</v>
+        <v>0.318232</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>3.067095</v>
+        <v>1.927155</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.042169</v>
+        <v>-0.943982</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.001169</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>1.670408</v>
+        <v>0.656291</v>
       </c>
       <c r="J118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>1.542149</v>
+        <v>1.098733</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.13975</v>
       </c>
       <c r="M118" s="3" t="n">
         <v>0</v>
@@ -9042,7 +9042,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -10660,7 +10664,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -11690,7 +11698,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -12346,7 +12358,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" s="5" t="n">
         <v>5.992926</v>
       </c>
@@ -14162,7 +14178,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -17544,7 +17564,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -19840,7 +19864,11 @@
           <t>Exploration and evaluation asset expenditures (Note 5)</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -20030,7 +20058,11 @@
           <t>Exploration and evaluation asset expenditures (Note 6)</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VEC.H.xlsx
+++ b/output/pdf_financials_xlsx/VEC.H.xlsx
@@ -2362,10 +2362,10 @@
         <v>0.009990000000000001</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.067204</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.010742</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.061276</v>
@@ -2374,31 +2374,31 @@
         <v>0.906034</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.040826</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.111372</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.1762</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.014929</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.004212</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.02013</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.002384</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.020062</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.002646</v>
       </c>
     </row>
     <row r="35">
@@ -2472,10 +2472,10 @@
         <v>0.009990000000000001</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.067204</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.010742</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.061276</v>
@@ -2484,31 +2484,31 @@
         <v>0.906034</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.040826</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.111372</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.1762</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.014929</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.004212</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.02013</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.002384</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.020062</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.002646</v>
       </c>
     </row>
     <row r="37">
@@ -3132,10 +3132,10 @@
         <v>0.003792</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.179589</v>
+        <v>0.112385</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.061609</v>
+        <v>0.050867</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.02517</v>
@@ -3144,31 +3144,31 @@
         <v>0.007582</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.048533</v>
+        <v>0.007707</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.119496</v>
+        <v>0.008123999999999999</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.189322</v>
+        <v>0.013122</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.0243</v>
+        <v>0.009371000000000001</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.014304</v>
+        <v>0.010092</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.022292</v>
+        <v>0.002162</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.004982</v>
+        <v>0.002598</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.02191</v>
+        <v>0.001848</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.005089</v>
+        <v>0.002443</v>
       </c>
     </row>
     <row r="49">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">

--- a/output/pdf_financials_xlsx/VEC.H.xlsx
+++ b/output/pdf_financials_xlsx/VEC.H.xlsx
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.382517</v>
+        <v>-0.382517</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.583058</v>
+        <v>-0.583058</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -20154,7 +20154,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -34554,7 +34558,11 @@
           <t>Deferred income tax recovery (Note 10)</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -35990,7 +35998,11 @@
           <t>Deferred income tax recovery (Note 9)</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
